--- a/tests/reports/Selenium_Report.xlsx
+++ b/tests/reports/Selenium_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="207">
   <si>
     <t>Execution Date</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:25:32 PM</t>
+    <t>6/15/2026, 6:06:40 PM</t>
   </si>
   <si>
     <t>Chrome Web (Headless)</t>
@@ -53,7 +53,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>96.97%</t>
+    <t>96.77%</t>
   </si>
   <si>
     <t>00:01:55</t>
@@ -551,30 +551,6 @@
     <t>Budget Planner header is displayed</t>
   </si>
   <si>
-    <t>TC_BUDGET_032</t>
-  </si>
-  <si>
-    <t>Add budget category limit</t>
-  </si>
-  <si>
-    <t>Should add budget category limit successfully</t>
-  </si>
-  <si>
-    <t>New category limit added and displayed</t>
-  </si>
-  <si>
-    <t>TC_BUDGET_033</t>
-  </si>
-  <si>
-    <t>Verify budget progress calculation</t>
-  </si>
-  <si>
-    <t>Should verify budget progress calculation is correct</t>
-  </si>
-  <si>
-    <t>Progress percentage matches spending details</t>
-  </si>
-  <si>
     <t>Test Name</t>
   </si>
   <si>
@@ -605,7 +581,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:55:32.813Z</t>
+    <t>2026-06-15T12:36:40.760Z</t>
   </si>
   <si>
     <t>Perform Login Action</t>
@@ -1152,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1178,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1923,52 +1899,6 @@
       </c>
       <c r="G32" s="2" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1993,13 +1923,13 @@
         <v>14</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2007,13 +1937,13 @@
         <v>119</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2036,70 +1966,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2121,53 +2051,53 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
